--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A378E913-5003-45BF-B102-3A2AA37EDBEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E642EB-DED5-4BE0-80BF-FF49471EDABC}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="3" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>NewBudgetPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>InternalAmendmentType__c</t>
   </si>
 </sst>
 </file>
@@ -494,7 +497,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
@@ -524,6 +527,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E642EB-DED5-4BE0-80BF-FF49471EDABC}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1064210-F6FD-40BA-BB43-AEFCEFC4B8C8}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" activeTab="2" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>None</t>
-  </si>
-  <si>
-    <t>AmendmentType__c</t>
   </si>
   <si>
     <t>Scope of Work Change</t>
@@ -497,10 +494,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -508,10 +505,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -519,10 +516,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -554,87 +551,87 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>12345</v>
@@ -642,13 +639,13 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -681,10 +678,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -692,10 +689,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -703,10 +700,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -736,10 +733,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>400</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1064210-F6FD-40BA-BB43-AEFCEFC4B8C8}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4011367-C0BF-4574-8C28-1D80CC479C57}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" activeTab="2" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="2" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
     <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId2"/>
     <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId3"/>
     <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId4"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId5"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId6"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId7"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId8"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId9"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="71">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -114,19 +120,163 @@
   </si>
   <si>
     <t>InternalAmendmentType__c</t>
+  </si>
+  <si>
+    <t>fieldPurposeRTA__c</t>
+  </si>
+  <si>
+    <t>fieldImpact__c</t>
+  </si>
+  <si>
+    <t>Funding Change</t>
+  </si>
+  <si>
+    <t>ProjectTitle__c</t>
+  </si>
+  <si>
+    <t>GrantAbbreviation__c</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>ProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>BudgetCategoryPackage__c</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>fieldInternalOrganization__c</t>
+  </si>
+  <si>
+    <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
+  </si>
+  <si>
+    <t>Program__c</t>
+  </si>
+  <si>
+    <t>Automation Permanent Internal Program</t>
+  </si>
+  <si>
+    <t>ExternalOrganization__c</t>
+  </si>
+  <si>
+    <t>Test Automation Organization</t>
+  </si>
+  <si>
+    <t>IsMatchRequired__c</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>LaverageAllowed__c</t>
+  </si>
+  <si>
+    <t>IsProgramIncomeAnticipated__c</t>
+  </si>
+  <si>
+    <t>IsAdvancePermitted__c</t>
+  </si>
+  <si>
+    <t>IsBuildUpFunctionality__c</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>IsGoalsRequired__c</t>
+  </si>
+  <si>
+    <t>KPIsRequired__c</t>
+  </si>
+  <si>
+    <t>AreExpensesBuildIUpLevel__c</t>
+  </si>
+  <si>
+    <t>RiskAssessmentRequired__c</t>
+  </si>
+  <si>
+    <t>WBSRequired__c</t>
+  </si>
+  <si>
+    <t>FocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>GrantAwardDescription__c</t>
+  </si>
+  <si>
+    <t>Automation Test Description</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>BudgetPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>SubmissionTitle__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Payment Request </t>
+  </si>
+  <si>
+    <t>Frequency__c</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>ScheduleBase__c</t>
+  </si>
+  <si>
+    <t>Reporting Period</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>CalReportingStartDate__c</t>
+  </si>
+  <si>
+    <t>CalReportingEndDate__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Progress Report </t>
+  </si>
+  <si>
+    <t>Automation Execution Award for Amendment Request</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -149,13 +299,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,13 +626,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,7 +643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -500,7 +654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -511,7 +665,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -528,17 +682,108 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -549,7 +794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -560,7 +805,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -571,7 +816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -582,7 +827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -593,7 +838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -604,7 +849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -615,7 +860,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -626,7 +871,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -637,7 +882,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -656,13 +901,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -673,7 +918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -684,7 +929,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -695,7 +940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -714,13 +959,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -731,7 +976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -746,4 +991,460 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4011367-C0BF-4574-8C28-1D80CC479C57}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FCA330-6883-4624-A771-6D3188CB41A1}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="2" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="3" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="72">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -252,6 +252,9 @@
   </si>
   <si>
     <t>Automation Execution Award for Amendment Request</t>
+  </si>
+  <si>
+    <t>fieldBudgetPeriodComments__c</t>
   </si>
 </sst>
 </file>
@@ -958,7 +961,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -984,7 +987,18 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>400</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FCA330-6883-4624-A771-6D3188CB41A1}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F5D762-23FA-4AC4-9A85-5AE4AAE6F6E2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="3" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
@@ -17,12 +17,13 @@
     <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId2"/>
     <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId3"/>
     <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId4"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId5"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId6"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId7"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId8"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId9"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId10"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId5"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId6"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId7"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId8"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId9"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId10"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="77">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -255,6 +256,21 @@
   </si>
   <si>
     <t>fieldBudgetPeriodComments__c</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>TermsAgreement__c</t>
+  </si>
+  <si>
+    <t>I Agree</t>
+  </si>
+  <si>
+    <t>ReceiptsUploaded__c</t>
+  </si>
+  <si>
+    <t>Checked</t>
   </si>
 </sst>
 </file>
@@ -686,6 +702,97 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -987,7 +1094,7 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1008,6 +1115,53 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1066,7 +1220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1179,7 +1333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1325,7 +1479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1370,95 +1524,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F5D762-23FA-4AC4-9A85-5AE4AAE6F6E2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619D12A6-FA9A-4DA6-805C-D523B0CE21D5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="3" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="75">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -121,12 +121,6 @@
   </si>
   <si>
     <t>InternalAmendmentType__c</t>
-  </si>
-  <si>
-    <t>fieldPurposeRTA__c</t>
-  </si>
-  <si>
-    <t>fieldImpact__c</t>
   </si>
   <si>
     <t>Funding Change</t>
@@ -645,13 +639,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -662,7 +656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -673,7 +667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -684,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -704,13 +698,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -721,67 +715,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>60</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>62</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>64</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -795,13 +789,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -812,67 +806,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>60</v>
       </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>62</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>64</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -886,14 +880,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -904,7 +898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -915,7 +909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -926,7 +920,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -937,7 +931,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -948,7 +942,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -959,7 +953,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -970,7 +964,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -981,7 +975,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -992,7 +986,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1011,13 +1005,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1028,7 +1022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1039,7 +1033,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1050,7 +1044,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1069,13 +1063,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1086,7 +1080,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1097,15 +1091,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1117,13 +1111,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1134,26 +1128,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
         <v>72</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
         <v>73</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1164,13 +1158,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1181,34 +1175,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>27</v>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>28</v>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1223,13 +1217,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1240,92 +1234,92 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1336,13 +1330,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1353,125 +1347,125 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>43</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
         <v>47</v>
       </c>
-      <c r="C5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>53</v>
       </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1482,13 +1476,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1499,23 +1493,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>56</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
       </c>
       <c r="C3">
         <v>3650</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619D12A6-FA9A-4DA6-805C-D523B0CE21D5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA28626-B98F-4FAD-AD06-96A4EEB9DD5D}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA28626-B98F-4FAD-AD06-96A4EEB9DD5D}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DB6DA1-3C54-47C6-8C47-8F22B6CA794F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="10" activeTab="12" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,8 @@
     <sheet name="Edition_Standalone" sheetId="8" r:id="rId9"/>
     <sheet name="Payment Request Schedule" sheetId="9" r:id="rId10"/>
     <sheet name="Progress Report Schedule" sheetId="10" r:id="rId11"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId12"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="79">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -265,6 +267,18 @@
   </si>
   <si>
     <t>Checked</t>
+  </si>
+  <si>
+    <t>Periodic Renewal</t>
+  </si>
+  <si>
+    <t>ProposedBPStartDate__c</t>
+  </si>
+  <si>
+    <t>ProposedBudgetEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldRequestedChangeInBudget__c</t>
   </si>
 </sst>
 </file>
@@ -639,13 +653,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -656,7 +670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -667,7 +681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -678,7 +692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -698,13 +712,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -715,7 +729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -726,7 +740,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -737,7 +751,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -748,7 +762,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -759,7 +773,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -770,7 +784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -789,13 +803,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -806,7 +820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -817,7 +831,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -828,7 +842,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -839,7 +853,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -850,7 +864,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -861,7 +875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -874,20 +888,137 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -898,7 +1029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -909,7 +1040,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -920,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -931,7 +1062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -942,7 +1073,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -953,7 +1084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -964,7 +1095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -975,7 +1106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -986,7 +1117,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1005,13 +1136,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1022,7 +1153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1033,7 +1164,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1044,7 +1175,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1063,13 +1194,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1080,7 +1211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1091,7 +1222,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1111,13 +1242,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1128,7 +1259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1139,7 +1270,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1158,13 +1289,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1175,7 +1306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1186,7 +1317,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1197,7 +1328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1217,13 +1348,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1234,7 +1365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1245,7 +1376,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1256,7 +1387,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1267,7 +1398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1278,7 +1409,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1289,7 +1420,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1300,7 +1431,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1311,7 +1442,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1330,13 +1461,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1347,7 +1478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1358,7 +1489,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1369,7 +1500,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1380,7 +1511,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1391,7 +1522,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1402,7 +1533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1413,7 +1544,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1424,7 +1555,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1435,7 +1566,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1446,7 +1577,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1457,7 +1588,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1476,13 +1607,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1493,7 +1624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1504,7 +1635,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>56</v>
       </c>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DB6DA1-3C54-47C6-8C47-8F22B6CA794F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E61ADF3-EAA2-4C5B-AFC8-4D03FB3C331A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="10" activeTab="12" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Automation_Product\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E61ADF3-EAA2-4C5B-AFC8-4D03FB3C331A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888E3D2F-9D18-492E-84C9-79D8EBA94FCE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="10" activeTab="12" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="11" activeTab="13" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="Progress Report Schedule" sheetId="10" r:id="rId11"/>
     <sheet name="Periodic Renewal" sheetId="12" r:id="rId12"/>
     <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId13"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="80">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -279,6 +280,9 @@
   </si>
   <si>
     <t>fieldRequestedChangeInBudget__c</t>
+  </si>
+  <si>
+    <t>Terms and Conditions Change</t>
   </si>
 </sst>
 </file>
@@ -653,13 +657,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -670,7 +674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -681,7 +685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -692,7 +696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -712,13 +716,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,7 +733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -740,7 +744,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -751,7 +755,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -762,7 +766,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -773,7 +777,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -784,7 +788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -803,13 +807,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -820,7 +824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -831,7 +835,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -842,7 +846,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -853,7 +857,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -864,7 +868,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -875,7 +879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -894,13 +898,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -911,7 +915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -922,7 +926,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -933,7 +937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -952,13 +956,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -969,7 +973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -980,7 +984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -991,7 +995,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1008,17 +1012,75 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1029,7 +1091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1040,7 +1102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1051,7 +1113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1062,7 +1124,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1073,7 +1135,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1084,7 +1146,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1095,7 +1157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1106,7 +1168,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1117,7 +1179,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1136,13 +1198,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1153,7 +1215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1164,7 +1226,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1175,7 +1237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1194,13 +1256,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1211,7 +1273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1222,7 +1284,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1242,13 +1304,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1259,7 +1321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1270,7 +1332,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1289,13 +1351,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1317,7 +1379,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1328,7 +1390,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1348,13 +1410,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1365,7 +1427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1376,7 +1438,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1387,7 +1449,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1398,7 +1460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1409,7 +1471,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1420,7 +1482,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1431,7 +1493,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1442,7 +1504,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1461,13 +1523,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1478,7 +1540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1489,7 +1551,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1500,7 +1562,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1511,7 +1573,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1522,7 +1584,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1533,7 +1595,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1544,7 +1606,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1555,7 +1617,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1566,7 +1628,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1577,7 +1639,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1588,7 +1650,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1607,13 +1669,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1624,7 +1686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1635,7 +1697,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>56</v>
       </c>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,32 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Automation_Product\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888E3D2F-9D18-492E-84C9-79D8EBA94FCE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B5870D-B9DA-4C0D-8D7F-2EC0C3F8A516}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="11" activeTab="13" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="2846" yWindow="2846" windowWidth="16457" windowHeight="8554" activeTab="1" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId2"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId3"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId4"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId5"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId6"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId7"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId8"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId9"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId10"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId11"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId12"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId13"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId14"/>
+    <sheet name="Budget_Redirection" sheetId="15" r:id="rId2"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId3"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId4"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId5"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId6"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId7"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId8"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId9"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId10"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId11"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId12"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId13"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId14"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="81">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -283,6 +284,9 @@
   </si>
   <si>
     <t>Terms and Conditions Change</t>
+  </si>
+  <si>
+    <t>Budget Redirection</t>
   </si>
 </sst>
 </file>
@@ -657,13 +661,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="2" max="2" width="28.23046875" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -674,7 +678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -685,7 +689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -696,7 +700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -714,15 +718,15 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -733,69 +737,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7">
+        <v>57</v>
+      </c>
+      <c r="C3">
         <v>3650</v>
       </c>
     </row>
@@ -805,15 +765,106 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.53515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -824,7 +875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -835,7 +886,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -846,7 +897,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -857,7 +908,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -868,7 +919,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -879,7 +930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -895,16 +946,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.4609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -915,7 +966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -926,7 +977,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -937,7 +988,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -953,16 +1004,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.4609375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -973,7 +1024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -984,7 +1035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -995,7 +1046,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1012,16 +1063,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.6328125" customWidth="1"/>
+    <col min="2" max="2" width="24.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.61328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1032,7 +1083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1043,7 +1094,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1054,7 +1105,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1071,16 +1122,76 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="7.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.23046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.23046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.23046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1091,7 +1202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1102,7 +1213,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1113,7 +1224,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1124,7 +1235,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1135,7 +1246,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1146,7 +1257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1157,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1168,7 +1279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1179,7 +1290,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1195,16 +1306,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.84375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1215,7 +1326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1226,7 +1337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1237,7 +1348,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1253,16 +1364,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,7 +1384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1284,7 +1395,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1301,16 +1412,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.69140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1321,7 +1432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1332,7 +1443,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1348,16 +1459,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.4609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1368,7 +1479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1379,7 +1490,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1390,7 +1501,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1407,16 +1518,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1427,7 +1538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1438,7 +1549,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1449,7 +1560,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1460,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1471,7 +1582,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1482,7 +1593,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1493,7 +1604,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1504,7 +1615,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1520,16 +1631,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.23046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1540,7 +1651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1551,7 +1662,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1562,7 +1673,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1573,7 +1684,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1584,7 +1695,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1595,7 +1706,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1606,7 +1717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1617,7 +1728,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1628,7 +1739,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1639,7 +1750,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1650,7 +1761,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1659,53 +1770,6 @@
       </c>
       <c r="C12" t="s">
         <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3">
-        <v>3650</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B5870D-B9DA-4C0D-8D7F-2EC0C3F8A516}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A61B4E7-C495-476A-B285-5E6E8AF5BF2F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2846" yWindow="2846" windowWidth="16457" windowHeight="8554" activeTab="1" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="13" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="80">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -272,9 +272,6 @@
   </si>
   <si>
     <t>Periodic Renewal</t>
-  </si>
-  <si>
-    <t>ProposedBPStartDate__c</t>
   </si>
   <si>
     <t>ProposedBudgetEndDate__c</t>
@@ -293,7 +290,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,6 +308,13 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF454545"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -334,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -345,6 +349,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -661,13 +668,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="28.23046875" customWidth="1"/>
+    <col min="2" max="2" width="28.19921875" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -689,7 +696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -700,7 +707,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -720,13 +727,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,7 +744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -748,7 +755,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -767,13 +774,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -784,7 +791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -795,7 +802,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -806,7 +813,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -817,7 +824,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -828,7 +835,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -839,7 +846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -858,13 +865,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -875,7 +882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -886,7 +893,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -897,7 +904,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -908,7 +915,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -919,7 +926,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -930,7 +937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -949,13 +956,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="26.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -966,7 +973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -977,7 +984,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -988,7 +995,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1006,14 +1013,14 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="23.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.46484375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1024,18 +1031,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C2" s="5">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1043,17 +1050,6 @@
         <v>77</v>
       </c>
       <c r="C3">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4">
         <v>1000</v>
       </c>
     </row>
@@ -1066,13 +1062,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="24.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.61328125" customWidth="1"/>
+    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,7 +1079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1091,10 +1087,10 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1105,7 +1101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1124,14 +1120,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.23046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1142,7 +1138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1150,10 +1146,10 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1164,7 +1160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1184,14 +1180,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.23046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.23046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1202,7 +1198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1213,7 +1209,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1224,7 +1220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1235,7 +1231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1246,7 +1242,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1257,7 +1253,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1268,7 +1264,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1279,7 +1275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1290,7 +1286,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1309,13 +1305,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="17.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.86328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1326,7 +1322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1337,7 +1333,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1348,7 +1344,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1367,13 +1363,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="25.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1384,7 +1380,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1395,7 +1391,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1415,13 +1411,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="20.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1432,7 +1428,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1443,7 +1439,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1462,13 +1458,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="26.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1479,7 +1475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1490,7 +1486,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1501,7 +1497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1521,13 +1517,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="29.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1538,7 +1534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1549,7 +1545,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1560,7 +1556,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1571,7 +1567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1582,7 +1578,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1593,7 +1589,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1604,7 +1600,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1615,7 +1611,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1634,13 +1630,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="30.23046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1651,7 +1647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1662,7 +1658,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1673,7 +1669,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1684,7 +1680,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1695,7 +1691,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1706,7 +1702,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1717,7 +1713,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1728,7 +1724,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1739,7 +1735,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1750,7 +1746,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1761,7 +1757,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,26 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A61B4E7-C495-476A-B285-5E6E8AF5BF2F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5C394D-86F4-4EDE-97C9-883B7F7732B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="13" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="8" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Budget_Redirection" sheetId="15" r:id="rId2"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId3"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId4"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId5"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId6"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId7"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId8"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId9"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId10"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId11"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId12"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId13"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId14"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId15"/>
+    <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId2"/>
+    <sheet name="Budget_Redirection" sheetId="15" r:id="rId3"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId4"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId5"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId6"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId7"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId8"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId9"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId10"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId11"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId12"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId13"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId14"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId15"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId16"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId17"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId18"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="86">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -284,13 +288,31 @@
   </si>
   <si>
     <t>Budget Redirection</t>
+  </si>
+  <si>
+    <t>fieldSubAmendmentType__c</t>
+  </si>
+  <si>
+    <t>fieldPurposeRTA__c</t>
+  </si>
+  <si>
+    <t>fieldImpact__c</t>
+  </si>
+  <si>
+    <t>fieldScopeofWorkChangeDescription__c</t>
+  </si>
+  <si>
+    <t>fieldCongressionaldistrict__c</t>
+  </si>
+  <si>
+    <t>fieldNewBudgetPeriodEndDate__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,6 +339,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="5"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -338,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -353,6 +381,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -725,6 +754,371 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="26.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.46484375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="30.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -771,7 +1165,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -862,7 +1256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -953,7 +1347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1011,7 +1405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1059,7 +1453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1118,6 +1512,66 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1177,7 +1631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1302,7 +1756,132 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.9296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1360,7 +1939,66 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1408,60 +2046,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="26.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -1477,295 +2069,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="30.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,30 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5C394D-86F4-4EDE-97C9-883B7F7732B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05429BAD-1508-4A5D-AB63-DFD720BA9046}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="8" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="2" activeTab="4" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId2"/>
     <sheet name="Budget_Redirection" sheetId="15" r:id="rId3"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId4"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId5"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId6"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId7"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId8"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId9"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId10"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId11"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId12"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId13"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId14"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId15"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId16"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId17"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId18"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId19"/>
+    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId4"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId5"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId6"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId7"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId8"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId9"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId10"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId11"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId12"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId13"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId14"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId15"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId16"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId17"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId18"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId19"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId20"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="87">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -306,6 +308,9 @@
   </si>
   <si>
     <t>fieldNewBudgetPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>Key Personnel Change</t>
   </si>
 </sst>
 </file>
@@ -754,6 +759,102 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="25.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.53125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -800,7 +901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -859,7 +960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -972,7 +1073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1118,7 +1219,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1165,7 +1266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1256,7 +1357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1347,7 +1448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1376,112 +1477,6 @@
       </c>
       <c r="C2" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="30.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="5">
-        <v>4017</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -1571,6 +1566,112 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="30.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="5">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
@@ -1632,6 +1733,123 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="23.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1756,7 +1974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1881,7 +2099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1939,7 +2157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1996,100 +2214,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="25.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.53125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05429BAD-1508-4A5D-AB63-DFD720BA9046}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771A19B6-4E6A-4E9B-8230-1166389000AC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="2" activeTab="4" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="9" activeTab="11" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -24,16 +24,17 @@
     <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId9"/>
     <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId10"/>
     <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId11"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId12"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId13"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId14"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId15"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId16"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId17"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId18"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId19"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId20"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId21"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId12"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId13"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId14"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId15"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId16"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId17"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId18"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId19"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId20"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId21"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="88">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -311,6 +312,9 @@
   </si>
   <si>
     <t>Key Personnel Change</t>
+  </si>
+  <si>
+    <t>Carry Forward</t>
   </si>
 </sst>
 </file>
@@ -855,6 +859,64 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -901,7 +963,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -960,7 +1022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1073,7 +1135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1219,7 +1281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1266,7 +1328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1357,7 +1419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1441,64 +1503,6 @@
       </c>
       <c r="C7">
         <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="26.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.46484375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1567,6 +1571,64 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="26.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.46484375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1614,7 +1676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771A19B6-4E6A-4E9B-8230-1166389000AC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96886475-6747-41B7-93AC-0A164D74A50C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="9" activeTab="11" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="18" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="89">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>Carry Forward</t>
+  </si>
+  <si>
+    <t>fieldInternalAmendmentType__c</t>
   </si>
 </sst>
 </file>
@@ -1595,7 +1598,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
@@ -1606,7 +1609,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1617,7 +1620,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96886475-6747-41B7-93AC-0A164D74A50C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EB9266-150F-46CC-A2B2-F2D2C6DEFD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="18" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -318,13 +318,22 @@
   </si>
   <si>
     <t>fieldInternalAmendmentType__c</t>
+  </si>
+  <si>
+    <t>fieldCountry__c</t>
+  </si>
+  <si>
+    <t>fieldCounty__c</t>
+  </si>
+  <si>
+    <t>Automation Country</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,6 +366,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -378,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -394,6 +409,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -709,13 +725,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.19921875" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -726,7 +742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -737,7 +753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -748,7 +764,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -768,13 +784,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -785,7 +801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -796,7 +812,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -816,14 +832,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -834,7 +850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -845,7 +861,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -864,13 +880,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -881,7 +897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -892,7 +908,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -903,7 +919,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -922,13 +938,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -939,7 +955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -950,7 +966,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -969,13 +985,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -986,7 +1002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -997,7 +1013,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1008,7 +1024,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1028,13 +1044,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1045,7 +1061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1056,7 +1072,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1067,7 +1083,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1078,7 +1094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1089,7 +1105,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1100,7 +1116,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1111,7 +1127,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1122,7 +1138,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1141,13 +1157,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1158,7 +1174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1169,7 +1185,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1180,7 +1196,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1191,7 +1207,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1202,7 +1218,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1213,7 +1229,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1224,7 +1240,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1235,7 +1251,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1246,7 +1262,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1257,7 +1273,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1268,7 +1284,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1287,13 +1303,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1304,7 +1320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1315,7 +1331,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -1334,13 +1350,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1351,7 +1367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1362,7 +1378,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1373,7 +1389,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1384,7 +1400,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1395,7 +1411,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1406,7 +1422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1425,13 +1441,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1442,7 +1458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1453,7 +1469,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1464,7 +1480,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1475,7 +1491,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1486,7 +1502,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1497,7 +1513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1516,14 +1532,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1534,7 +1550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1545,7 +1561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1556,7 +1572,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1576,13 +1592,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1593,7 +1609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1604,7 +1620,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1615,7 +1631,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1634,13 +1650,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1651,7 +1667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1662,7 +1678,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1682,13 +1698,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.59765625" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1699,7 +1715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1710,7 +1726,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1721,7 +1737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1740,14 +1756,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1758,7 +1774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1769,7 +1785,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1780,7 +1796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1800,13 +1816,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1817,7 +1833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1828,7 +1844,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1839,7 +1855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1859,13 +1875,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1876,7 +1892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1887,7 +1903,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1898,7 +1914,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1916,15 +1932,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1935,7 +1951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1946,7 +1962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1957,7 +1973,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1968,7 +1984,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1979,7 +1995,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1990,7 +2006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2001,18 +2017,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -2023,7 +2039,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2032,6 +2048,17 @@
       </c>
       <c r="C10" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2042,14 +2069,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.9296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2060,7 +2087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2071,7 +2098,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2082,7 +2109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2093,7 +2120,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2104,7 +2131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2115,7 +2142,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2126,7 +2153,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2137,7 +2164,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -2148,7 +2175,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2167,13 +2194,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2184,7 +2211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2195,7 +2222,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2206,7 +2233,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2225,13 +2252,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2242,7 +2269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2253,7 +2280,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2264,7 +2291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EB9266-150F-46CC-A2B2-F2D2C6DEFD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E880B3-FD77-493C-800E-5082DF4E02EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="18" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="96">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -327,6 +327,18 @@
   </si>
   <si>
     <t>Automation Country</t>
+  </si>
+  <si>
+    <t>KA</t>
+  </si>
+  <si>
+    <t>fieldState__c</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>VA</t>
   </si>
 </sst>
 </file>
@@ -1649,7 +1661,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
@@ -1687,6 +1699,50 @@
       </c>
       <c r="C3">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E880B3-FD77-493C-800E-5082DF4E02EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A4FF53-DA2F-423B-98E7-6D16BDADC3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="18" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
@@ -281,9 +281,6 @@
     <t>Periodic Renewal</t>
   </si>
   <si>
-    <t>ProposedBudgetEndDate__c</t>
-  </si>
-  <si>
     <t>fieldRequestedChangeInBudget__c</t>
   </si>
   <si>
@@ -339,6 +336,9 @@
   </si>
   <si>
     <t>VA</t>
+  </si>
+  <si>
+    <t>fieldProposedBudgetEndDate__c</t>
   </si>
 </sst>
 </file>
@@ -867,7 +867,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -914,10 +914,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -925,7 +925,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -936,7 +936,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1567,7 +1567,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1578,7 +1578,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1589,7 +1589,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
@@ -1637,7 +1637,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1648,7 +1648,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1661,10 +1661,10 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1683,8 +1683,8 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>76</v>
+      <c r="B2" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
@@ -1695,7 +1695,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -1706,7 +1706,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
         <v>30</v>
@@ -1717,10 +1717,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1728,10 +1728,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1739,11 +1739,14 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" t="s">
         <v>93</v>
       </c>
-      <c r="C7" t="s">
-        <v>94</v>
-      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1779,7 +1782,7 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1838,7 +1841,7 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1894,10 +1897,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1905,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1916,7 +1919,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1953,10 +1956,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1964,7 +1967,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1975,7 +1978,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2078,10 +2081,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2111,7 +2114,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -2148,7 +2151,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -2236,7 +2239,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -2330,7 +2333,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
@@ -2341,7 +2344,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2352,7 +2355,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A4FF53-DA2F-423B-98E7-6D16BDADC3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BA0522-3DDC-46C0-92C6-AC53D5E5AFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="18" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -126,9 +126,6 @@
   </si>
   <si>
     <t>Budget Period Change</t>
-  </si>
-  <si>
-    <t>NewBudgetPeriodEndDate__c</t>
   </si>
   <si>
     <t>InternalAmendmentType__c</t>
@@ -759,7 +756,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -817,8 +814,8 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
-        <v>25</v>
+      <c r="B2" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -829,10 +826,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -867,7 +864,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -878,10 +875,10 @@
         <v>12</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -914,10 +911,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -925,7 +922,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -936,7 +933,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -969,24 +966,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
         <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1019,10 +1016,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
         <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1078,10 +1075,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1089,10 +1086,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
         <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1100,7 +1097,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1111,7 +1108,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1122,10 +1119,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1133,10 +1130,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
         <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1144,10 +1141,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
         <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1155,10 +1152,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1191,10 +1188,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1202,10 +1199,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1213,10 +1210,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1224,10 +1221,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1235,10 +1232,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1246,10 +1243,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1257,10 +1254,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1268,10 +1265,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1279,10 +1276,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1290,10 +1287,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1301,10 +1298,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1337,18 +1334,18 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
         <v>54</v>
-      </c>
-      <c r="C2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
         <v>56</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
       </c>
       <c r="C3">
         <v>3650</v>
@@ -1384,10 +1381,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
         <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1395,10 +1392,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
         <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1406,10 +1403,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
         <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1417,10 +1414,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1428,7 +1425,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1439,7 +1436,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1475,10 +1472,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1486,10 +1483,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
         <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1497,10 +1494,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
         <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1508,10 +1505,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1519,7 +1516,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1530,7 +1527,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1567,7 +1564,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1578,7 +1575,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1589,7 +1586,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1626,10 +1623,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1637,7 +1634,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1648,7 +1645,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1684,7 +1681,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
@@ -1695,7 +1692,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -1706,10 +1703,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1717,10 +1714,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1728,10 +1725,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1739,10 +1736,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
         <v>92</v>
-      </c>
-      <c r="C7" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1779,10 +1776,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1838,10 +1835,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1897,10 +1894,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1908,7 +1905,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1919,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1956,10 +1953,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1967,7 +1964,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1978,7 +1975,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2081,10 +2078,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2114,7 +2111,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -2151,7 +2148,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -2239,7 +2236,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -2275,7 +2272,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
@@ -2333,7 +2330,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
@@ -2344,7 +2341,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2355,7 +2352,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BA0522-3DDC-46C0-92C6-AC53D5E5AFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B50D16-2CF6-4F72-BEEF-0CA7E849C10C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="18" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="0" yWindow="390" windowWidth="20490" windowHeight="10920" firstSheet="20" activeTab="21" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,8 @@
     <sheet name="Progress Report Schedule" sheetId="10" r:id="rId19"/>
     <sheet name="Periodic Renewal" sheetId="12" r:id="rId20"/>
     <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId21"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId22"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId22"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1752,6 +1753,75 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,41 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B50D16-2CF6-4F72-BEEF-0CA7E849C10C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D876934B-224D-4270-A86D-363FFB607931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="20490" windowHeight="10920" firstSheet="20" activeTab="21" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="9" activeTab="11" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId2"/>
-    <sheet name="Budget_Redirection" sheetId="15" r:id="rId3"/>
-    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId4"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId5"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId6"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId7"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId8"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId9"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId10"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId11"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId12"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId13"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId14"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId15"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId16"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId17"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId18"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId19"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId20"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId21"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId22"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId23"/>
+    <sheet name="Scope&amp;BudgetPeriod_Creation" sheetId="25" r:id="rId2"/>
+    <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId3"/>
+    <sheet name="Budget_Redirection" sheetId="15" r:id="rId4"/>
+    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId5"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId6"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId7"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId8"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId9"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId10"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId11"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId12"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId13"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId14"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId15"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId16"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId17"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId18"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId19"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId20"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId21"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId22"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId23"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,6 +46,11 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -52,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -792,6 +798,65 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -839,7 +904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -887,7 +952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -945,7 +1010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -992,7 +1057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1051,7 +1116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1164,7 +1229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1310,7 +1375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1357,7 +1422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1448,7 +1513,76 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1539,7 +1673,287 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="5">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1599,287 +2013,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="5">
-        <v>4017</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="7"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1939,7 +2073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1998,7 +2132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2056,7 +2190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2192,7 +2326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2317,7 +2451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2373,63 +2507,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D876934B-224D-4270-A86D-363FFB607931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DB6404-8D7F-4F1E-821C-42D2AC4EB51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="9" activeTab="11" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="15" yWindow="0" windowWidth="20490" windowHeight="10920" firstSheet="8" activeTab="10" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -23,20 +23,21 @@
     <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId8"/>
     <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId9"/>
     <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId10"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId11"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId12"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId13"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId14"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId15"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId16"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId17"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId18"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId19"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId20"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId21"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId22"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId23"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId24"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId11"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId12"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId13"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId14"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId15"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId16"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId17"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId18"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId19"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId20"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId21"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId22"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId23"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId24"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="98">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -117,9 +118,6 @@
     <t>Automation City</t>
   </si>
   <si>
-    <t>County__c</t>
-  </si>
-  <si>
     <t>Automation County</t>
   </si>
   <si>
@@ -343,6 +341,18 @@
   </si>
   <si>
     <t>fieldProposedBudgetEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldCity__c</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>fieldAddressline1__c</t>
+  </si>
+  <si>
+    <t>fieldAddressline2__c</t>
   </si>
 </sst>
 </file>
@@ -763,7 +773,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -822,10 +832,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -833,7 +843,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -844,7 +854,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -857,6 +867,75 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -881,7 +960,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -892,10 +971,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -904,7 +983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -930,7 +1009,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -941,10 +1020,10 @@
         <v>12</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -952,7 +1031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -977,10 +1056,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -988,7 +1067,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -999,7 +1078,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1010,7 +1089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1032,24 +1111,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" t="s">
         <v>69</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
         <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1082,10 +1161,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
         <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1116,7 +1195,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1141,10 +1220,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1152,10 +1231,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
         <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1163,7 +1242,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1174,7 +1253,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1185,10 +1264,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
         <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1196,10 +1275,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
         <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1207,10 +1286,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
         <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1218,10 +1297,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
         <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1229,7 +1308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1254,10 +1333,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1265,10 +1344,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1276,10 +1355,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1287,10 +1366,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1298,10 +1377,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1309,10 +1388,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1320,10 +1399,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1331,10 +1410,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1342,10 +1421,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1353,10 +1432,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1364,10 +1443,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1375,7 +1454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1400,111 +1479,20 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
         <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
-        <v>56</v>
-      </c>
       <c r="C3">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7">
         <v>3650</v>
       </c>
     </row>
@@ -1538,7 +1526,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1549,10 +1537,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1583,6 +1571,97 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1607,10 +1686,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1618,10 +1697,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
         <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1629,10 +1708,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
         <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1640,10 +1719,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1651,7 +1730,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1662,7 +1741,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1673,7 +1752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1698,10 +1777,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1709,7 +1788,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1720,7 +1799,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1731,7 +1810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1756,7 +1835,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
@@ -1767,7 +1846,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -1778,10 +1857,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1789,10 +1868,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1800,10 +1879,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1811,10 +1890,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
         <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1826,7 +1905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1851,10 +1930,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
         <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1862,10 +1941,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1895,7 +1974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1920,10 +1999,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1979,7 +2058,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1990,7 +2069,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2001,7 +2080,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2039,10 +2118,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2098,10 +2177,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2109,7 +2188,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2120,7 +2199,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2157,10 +2236,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2168,7 +2247,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2179,7 +2258,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2282,10 +2361,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2293,7 +2372,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <v>12345</v>
@@ -2304,10 +2383,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2315,10 +2394,10 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2332,7 +2411,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2352,7 +2431,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -2362,8 +2441,8 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
+      <c r="B3" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -2373,44 +2452,44 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
+      <c r="B4" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
+      <c r="B5" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
+      <c r="B6" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>17</v>
+      <c r="B7" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2418,32 +2497,32 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
         <v>20</v>
+      </c>
+      <c r="C8">
+        <v>12345</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9">
-        <v>12345</v>
+      <c r="B9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>82</v>
+      <c r="B10" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2476,10 +2555,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DB6404-8D7F-4F1E-821C-42D2AC4EB51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C81D136-3BD0-42E4-96C1-6CAF8B82AC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="0" windowWidth="20490" windowHeight="10920" firstSheet="8" activeTab="10" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="22" activeTab="23" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C81D136-3BD0-42E4-96C1-6CAF8B82AC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EF3AD2-3800-4A98-A82C-02E84AD89AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="22" activeTab="23" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-90" yWindow="15" windowWidth="20490" windowHeight="10920" firstSheet="23" activeTab="25" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,7 @@
     <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId23"/>
     <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId24"/>
     <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId25"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="98">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -359,7 +360,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,6 +399,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1B1B1B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -419,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -436,6 +443,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2032,6 +2040,97 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EF3AD2-3800-4A98-A82C-02E84AD89AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A62760-921C-4DF1-900B-CF8B012E1A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="15" windowWidth="20490" windowHeight="10920" firstSheet="23" activeTab="25" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="30" yWindow="15" windowWidth="20490" windowHeight="10920" firstSheet="21" activeTab="23" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -36,9 +36,10 @@
     <sheet name="Progress Report Schedule" sheetId="10" r:id="rId21"/>
     <sheet name="Periodic Renewal" sheetId="12" r:id="rId22"/>
     <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId23"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId24"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId25"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId26"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId24"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId25"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId26"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="98">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1914,6 +1915,97 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="5">
+        <v>6017</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1982,7 +2074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2040,7 +2132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A62760-921C-4DF1-900B-CF8B012E1A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BAA6D4-CB47-4B5D-B7CE-B480B52AF3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="15" windowWidth="20490" windowHeight="10920" firstSheet="21" activeTab="23" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="75" yWindow="0" windowWidth="20490" windowHeight="10920" firstSheet="10" activeTab="10" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BAA6D4-CB47-4B5D-B7CE-B480B52AF3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D6A6BC-3D67-4B6A-A9BB-0A71E8239ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="75" yWindow="0" windowWidth="20490" windowHeight="10920" firstSheet="10" activeTab="10" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="135" yWindow="90" windowWidth="20370" windowHeight="10920" firstSheet="8" activeTab="9" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D6A6BC-3D67-4B6A-A9BB-0A71E8239ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AC21DB-7C51-42A7-AC4B-04F415D2A000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="90" windowWidth="20370" windowHeight="10920" firstSheet="8" activeTab="9" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="20" activeTab="22" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="99">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -355,6 +355,9 @@
   </si>
   <si>
     <t>fieldAddressline2__c</t>
+  </si>
+  <si>
+    <t>fieldRevisedCommitment__c</t>
   </si>
 </sst>
 </file>
@@ -1906,7 +1909,15 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="7"/>
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8">
+        <v>1000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation_allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AC21DB-7C51-42A7-AC4B-04F415D2A000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B516BD-004F-4D54-98DD-30065E369051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="20" activeTab="22" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="45" yWindow="0" windowWidth="20355" windowHeight="10920" firstSheet="20" activeTab="22" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -1916,7 +1916,7 @@
         <v>98</v>
       </c>
       <c r="C8">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation_allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B516BD-004F-4D54-98DD-30065E369051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A140D94B-49D0-4F50-92B0-9063A267D266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="0" windowWidth="20355" windowHeight="10920" firstSheet="20" activeTab="22" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="135" yWindow="390" windowWidth="20355" windowHeight="10920" firstSheet="21" activeTab="22" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="99">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1927,7 +1927,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
@@ -2009,6 +2009,17 @@
       </c>
       <c r="C7" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8">
+        <v>3000</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation_allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A140D94B-49D0-4F50-92B0-9063A267D266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6277D6-4BB6-4F22-B0F4-3B0178850DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="390" windowWidth="20355" windowHeight="10920" firstSheet="21" activeTab="22" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="135" yWindow="390" windowWidth="20355" windowHeight="10920" firstSheet="24" activeTab="25" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="97">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -129,9 +129,6 @@
     <t>Congressionaldistrict__c</t>
   </si>
   <si>
-    <t>1st District</t>
-  </si>
-  <si>
     <t>Budget Period Change</t>
   </si>
   <si>
@@ -328,9 +325,6 @@
   </si>
   <si>
     <t>Automation Country</t>
-  </si>
-  <si>
-    <t>KA</t>
   </si>
   <si>
     <t>fieldState__c</t>
@@ -754,7 +748,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -785,7 +779,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -844,10 +838,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -855,7 +849,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -866,7 +860,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -903,10 +897,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -914,7 +908,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -925,7 +919,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -936,7 +930,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -972,7 +966,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -983,10 +977,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1015,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -1032,10 +1026,10 @@
         <v>12</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1068,10 +1062,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1079,7 +1073,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1090,7 +1084,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1123,24 +1117,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
         <v>68</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
         <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1173,10 +1167,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1232,10 +1226,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1243,10 +1237,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
         <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1254,7 +1248,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1265,7 +1259,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1276,10 +1270,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
         <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1287,10 +1281,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1298,10 +1292,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1309,10 +1303,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
         <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1345,10 +1339,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1356,10 +1350,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1367,10 +1361,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1378,10 +1372,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1389,10 +1383,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1400,10 +1394,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1411,10 +1405,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1422,10 +1416,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1433,10 +1427,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1444,10 +1438,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1455,10 +1449,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1491,18 +1485,18 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
         <v>54</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
       </c>
       <c r="C3">
         <v>3650</v>
@@ -1538,7 +1532,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1549,10 +1543,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1607,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
         <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1618,10 +1612,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
         <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1629,10 +1623,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
         <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1640,10 +1634,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1651,7 +1645,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1662,7 +1656,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1698,10 +1692,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1709,10 +1703,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
         <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1720,10 +1714,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
         <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1731,10 +1725,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1742,7 +1736,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1753,7 +1747,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1789,10 +1783,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1800,7 +1794,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1811,7 +1805,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1847,7 +1841,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
@@ -1858,7 +1852,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -1869,10 +1863,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1880,10 +1874,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1891,10 +1885,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" t="s">
-        <v>89</v>
+        <v>80</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1902,10 +1896,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1913,7 +1907,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -1950,7 +1944,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C2" s="5">
         <v>6017</v>
@@ -1961,7 +1955,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -1972,10 +1966,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1983,10 +1977,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1994,10 +1988,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" t="s">
-        <v>89</v>
+        <v>80</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2005,10 +1999,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2016,7 +2010,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -2052,10 +2046,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2063,10 +2057,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2121,10 +2115,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2179,7 +2173,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -2190,10 +2184,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2201,10 +2195,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2212,10 +2206,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2271,7 +2265,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -2282,7 +2276,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2293,7 +2287,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2331,10 +2325,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2390,10 +2384,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2401,7 +2395,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2412,7 +2406,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2449,10 +2443,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2460,7 +2454,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2471,7 +2465,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2574,10 +2568,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2598,8 +2592,8 @@
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
-        <v>22</v>
+      <c r="C10">
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2607,7 +2601,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -2644,7 +2638,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -2655,7 +2649,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -2666,7 +2660,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -2677,7 +2671,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
@@ -2688,7 +2682,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2699,7 +2693,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -2721,10 +2715,10 @@
         <v>12</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
+        <v>80</v>
+      </c>
+      <c r="C9">
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2732,10 +2726,10 @@
         <v>12</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2768,10 +2762,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation_allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6277D6-4BB6-4F22-B0F4-3B0178850DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091B4903-1BC1-45F0-9509-668242BC5C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="390" windowWidth="20355" windowHeight="10920" firstSheet="24" activeTab="25" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="6" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -324,9 +324,6 @@
     <t>fieldCounty__c</t>
   </si>
   <si>
-    <t>Automation Country</t>
-  </si>
-  <si>
     <t>fieldState__c</t>
   </si>
   <si>
@@ -352,6 +349,9 @@
   </si>
   <si>
     <t>fieldRevisedCommitment__c</t>
+  </si>
+  <si>
+    <t>USA</t>
   </si>
 </sst>
 </file>
@@ -1841,7 +1841,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
@@ -1877,7 +1877,7 @@
         <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1896,10 +1896,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
         <v>88</v>
-      </c>
-      <c r="C7" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1907,7 +1907,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -1944,7 +1944,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C2" s="5">
         <v>6017</v>
@@ -1980,7 +1980,7 @@
         <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1999,10 +1999,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
         <v>88</v>
-      </c>
-      <c r="C7" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2010,7 +2010,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -2567,11 +2567,11 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="7" t="s">
         <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2660,7 +2660,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -2671,7 +2671,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
@@ -2682,7 +2682,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2729,7 +2729,7 @@
         <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation_allocation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Auto_Clone\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091B4903-1BC1-45F0-9509-668242BC5C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DAA2E2-A2BF-407D-BACA-567533A0F303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="6" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -18,28 +18,29 @@
     <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId3"/>
     <sheet name="Budget_Redirection" sheetId="15" r:id="rId4"/>
     <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId5"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId6"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId7"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId8"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId9"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId10"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId11"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId12"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId13"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId14"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId15"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId16"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId17"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId18"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId19"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId20"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId21"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId22"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId23"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId24"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId25"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId26"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId27"/>
+    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId6"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId7"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId8"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId9"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId10"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId11"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId12"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId13"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId14"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId15"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId16"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId17"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId18"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId19"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId20"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId21"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId22"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId23"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId24"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId25"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId26"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId27"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="97">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -748,7 +749,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -814,6 +815,64 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -872,7 +931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -941,7 +1000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -989,7 +1048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1037,7 +1096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1095,7 +1154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1142,7 +1201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1201,7 +1260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1314,7 +1373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1453,53 +1512,6 @@
       </c>
       <c r="C12" t="s">
         <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3">
-        <v>3650</v>
       </c>
     </row>
   </sheetData>
@@ -1577,6 +1589,53 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1667,7 +1726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1758,7 +1817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1816,7 +1875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1919,7 +1978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2021,7 +2080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2090,7 +2149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2148,7 +2207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2419,6 +2478,75 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2476,7 +2604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2612,7 +2740,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2735,62 +2863,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Auto_Clone\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DAA2E2-A2BF-407D-BACA-567533A0F303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1714E015-A17B-44CD-9415-E56035925263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="5085" yWindow="2100" windowWidth="15375" windowHeight="7875" firstSheet="6" activeTab="6" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -19,28 +19,31 @@
     <sheet name="Budget_Redirection" sheetId="15" r:id="rId4"/>
     <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId5"/>
     <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId6"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId7"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId8"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId9"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId10"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId11"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId12"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId13"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId14"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId15"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId16"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId17"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId18"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId19"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId20"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId21"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId22"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId23"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId24"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId25"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId26"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId27"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId28"/>
+    <sheet name="Subrecipient_BRedirec_SOW_KPC" sheetId="31" r:id="rId7"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId8"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId9"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="32" r:id="rId10"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId11"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId12"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId13"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId14"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId15"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId16"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId17"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId18"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId19"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId20"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId21"/>
+    <sheet name="Sheet1" sheetId="30" r:id="rId22"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId23"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId24"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId25"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId26"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId27"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId28"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId29"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId30"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="101">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -353,6 +356,18 @@
   </si>
   <si>
     <t>USA</t>
+  </si>
+  <si>
+    <t>Automation Justification for Key Personnel</t>
+  </si>
+  <si>
+    <t>Automation Justification for Budget Redirection</t>
+  </si>
+  <si>
+    <t>fieldJustification__c</t>
+  </si>
+  <si>
+    <t>fieldContactChangeDescription__c</t>
   </si>
 </sst>
 </file>
@@ -815,6 +830,290 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59AB248-7CC6-4163-8DB8-7AB3148833D0}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -872,7 +1171,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -931,7 +1230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1000,7 +1299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1048,7 +1347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1096,7 +1395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1154,7 +1453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1201,7 +1500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1257,265 +1556,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1589,6 +1629,274 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA489606-3595-4208-B63B-D607EB469F62}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1635,7 +1943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1726,7 +2034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1817,7 +2125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1875,7 +2183,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1978,7 +2286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2080,7 +2388,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2141,155 +2449,6 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2358,6 +2517,155 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
@@ -2547,6 +2855,86 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9509C983-4B94-4D59-AFC3-3D41924CAE8C}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2604,7 +2992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2738,129 +3126,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
-    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,39 +8,40 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Auto_Clone\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DAA2E2-A2BF-407D-BACA-567533A0F303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADCE21F-CCD9-43C0-A9FB-85698A4DC5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Scope&amp;BudgetPeriod_Creation" sheetId="25" r:id="rId2"/>
-    <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId3"/>
-    <sheet name="Budget_Redirection" sheetId="15" r:id="rId4"/>
-    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId5"/>
-    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId6"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId7"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId8"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId9"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId10"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId11"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId12"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId13"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId14"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId15"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId16"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId17"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId18"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId19"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId20"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId21"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId22"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId23"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId24"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId25"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId26"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId27"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId28"/>
+    <sheet name="BPC_SOW_FC_Creation" sheetId="30" r:id="rId3"/>
+    <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId4"/>
+    <sheet name="Budget_Redirection" sheetId="15" r:id="rId5"/>
+    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId6"/>
+    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId7"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId8"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId9"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId10"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId11"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId12"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId13"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId14"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId15"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId16"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId17"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId18"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId19"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId20"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId21"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId22"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId23"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId24"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId25"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId26"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId27"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId28"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="97">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -815,6 +816,131 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -872,7 +998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -931,7 +1057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1000,7 +1126,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1048,7 +1174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1096,7 +1222,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1154,7 +1280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1201,7 +1327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1260,7 +1386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1366,152 +1492,6 @@
       </c>
       <c r="C9" t="s">
         <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1589,6 +1569,152 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1635,7 +1761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1726,7 +1852,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1817,7 +1943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1875,7 +2001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1978,7 +2104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2080,7 +2206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2149,7 +2275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2207,7 +2333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2299,6 +2425,86 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2358,7 +2564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2418,7 +2624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2477,7 +2683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2546,7 +2752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2604,7 +2810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2738,129 +2944,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
-    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Auto_Clone\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADCE21F-CCD9-43C0-A9FB-85698A4DC5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98AA166-91E0-4F58-92C0-14DCADB4A3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="9" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -26,22 +26,23 @@
     <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId11"/>
     <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId12"/>
     <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId13"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId14"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId15"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId16"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId17"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId18"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId19"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId20"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId21"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId22"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId23"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId24"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId25"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId26"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId27"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId28"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId29"/>
+    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId14"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId15"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId16"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId17"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId18"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId19"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId20"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId21"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId22"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId23"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId24"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId25"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId26"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId27"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId28"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId29"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="97">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1127,6 +1128,85 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1174,7 +1254,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1222,7 +1302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1280,7 +1360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1327,7 +1407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1383,119 +1463,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1569,6 +1536,119 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1714,7 +1794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1761,7 +1841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1852,7 +1932,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1943,7 +2023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2001,7 +2081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2104,7 +2184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2206,7 +2286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2275,7 +2355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2325,97 +2405,6 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2496,6 +2485,97 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
         <v>6</v>
       </c>
     </row>
